--- a/rules/CORE-000222/positive/01/data/unit-test-coreid-CG0416-positive 1.xlsx
+++ b/rules/CORE-000222/positive/01/data/unit-test-coreid-CG0416-positive 1.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="suppae.xpt" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="suppdm.xpt" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,34 +28,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <i val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
-        <bgColor rgb="00FFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
-        <bgColor theme="0" tint="-0.1499984740745262"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -62,49 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,12 +420,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
@@ -508,16 +454,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Filename</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
@@ -532,6 +478,18 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>Supplemental Qualifiers for AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>suppdm.xpt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Supplemental Qualifiers for Demographics</t>
         </is>
       </c>
     </row>
@@ -546,694 +504,757 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>STUDYID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>RDOMAIN</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>USUBJID</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>IDVAR</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>IDVARVAL</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>QNAM</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>QLABEL</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>QVAL</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>QORIG</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>QEVAL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Related Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Identifying Variable</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Identifying Variable Value</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Qualifier Variable Name</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Qualifier Variable Label</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Data Value</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Evaluator</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" t="n">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" t="n">
         <v>14</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" t="n">
         <v>40</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" t="n">
         <v>19</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J4" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>CDISC-TEST</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>AE</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>CDISC-TEST-001</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>AESPID</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>DICTVER</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Dictionary Version</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>MEDDRA VERSION 22.0</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Assigned</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>CLINICAL STUDY SPONSOR</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>CDISC-TEST</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>AE</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>CDISC-TEST-001</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>AESPID</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AETRTEM</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Treatment Emergent Flag</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>STATISTICIAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CDISC-TEST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CDISC-TEST-001</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AESPID</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AECNTRL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Adverse Event Causality Control Code</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CRF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CDISC-TEST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CDISC-TEST-001</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AESPID</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AECMT</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A 40-char QLABEL valid boundary value!!!</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>See comment</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CRF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CDISC-TEST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CDISC-TEST-001</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AESPID</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>DICTVER</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Dictionary Version</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>MEDDRA VERSION 22.0</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Assigned</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>CLINICAL STUDY SPONSOR</t>
         </is>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>RDOMAIN</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>IDVAR</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>IDVARVAL</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>QNAM</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>QLABEL</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>QVAL</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>QORIG</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>QEVAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Study Identifier</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Related Domain Abbreviation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unique Subject Identifier</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Identifying Variable</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Identifying Variable Value</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Qualifier Variable Name</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Qualifier Variable Label</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Data Value</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Evaluator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40</v>
+      </c>
+      <c r="H4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CDISC008</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>RACE1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Race 1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CRF</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CDISC008</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RACE2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Race 2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>BLACK OR AFRICAN AMERICAN</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CRF</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>CDISC-TEST</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>CDISC-TEST-001</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>AESPID</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>DICTVER</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Dictionary Version</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>MEDDRA VERSION 22.0</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>CLINICAL STUDY SPONSOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>CDISC-TEST</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>CDISC-TEST-001</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>AESPID</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>DICTVER</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>Dictionary Version</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>MEDDRA VERSION 22.0</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>CLINICAL STUDY SPONSOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>CDISC-TEST</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>CDISC-TEST-001</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>AESPID</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>DICTVER</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Dictionary Version</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>MEDDRA VERSION 22.0</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>CLINICAL STUDY SPONSOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>CDISC-TEST</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>CDISC-TEST-001</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>AESPID</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>DICTVER</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>Dictionary Version</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>MEDDRA VERSION 22.0</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>CLINICAL STUDY SPONSOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>CDISC-TEST</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>CDISC-TEST-001</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>AESPID</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>DICTVER</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Dictionary Version</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>MEDDRA VERSION 22.0</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>CLINICAL STUDY SPONSOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>CDISC-TEST</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>CDISC-TEST-001</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>AESPID</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>DICTVER</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Dictionary Version</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>MEDDRA VERSION 22.0</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>CLINICAL STUDY SPONSOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>CDISC-TEST</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>CDISC-TEST-001</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>AESPID</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>DICTVER</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>DictionaryVersionDictionaryVersionVersio</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>MEDDRA VERSION 22.0</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>CLINICAL STUDY SPONSOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>CDISC-TEST</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>CDISC-TEST-001</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>AESPID</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>DICTVER</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Dictionary Version</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>MEDDRA VERSION 22.0</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>CLINICAL STUDY SPONSOR</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CDISC008</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>RACE3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Race 3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>WHITE</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CRF</t>
         </is>
       </c>
     </row>
